--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.70308939227126</v>
+        <v>4.176752026244079</v>
       </c>
       <c r="D2" t="n">
-        <v>26.47469595324303</v>
+        <v>4.302138092401992</v>
       </c>
       <c r="E2" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F2" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.28358287774662</v>
+        <v>12.72108221763383</v>
       </c>
       <c r="D3" t="n">
-        <v>78.49366753118242</v>
+        <v>12.75522097381714</v>
       </c>
       <c r="E3" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F3" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.76143287778532</v>
+        <v>2.561232842640114</v>
       </c>
       <c r="D4" t="n">
-        <v>13.50281034678096</v>
+        <v>2.194206681351907</v>
       </c>
       <c r="E4" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F4" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.89808168428437</v>
+        <v>2.90843827369621</v>
       </c>
       <c r="D5" t="n">
-        <v>18.55224686639653</v>
+        <v>3.014740115789436</v>
       </c>
       <c r="E5" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F5" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>84.08570063079419</v>
+        <v>13.66392635250406</v>
       </c>
       <c r="D6" t="n">
-        <v>84.17329521716114</v>
+        <v>13.67816047278869</v>
       </c>
       <c r="E6" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F6" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.967686333277015</v>
+        <v>1.619749029157515</v>
       </c>
       <c r="D7" t="n">
-        <v>12.46530967602462</v>
+        <v>2.025612822354001</v>
       </c>
       <c r="E7" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F7" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.876269776752201</v>
+        <v>0.7923938387222327</v>
       </c>
       <c r="D8" t="n">
-        <v>4.226131634236043</v>
+        <v>0.686746390563357</v>
       </c>
       <c r="E8" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F8" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.37189472815895</v>
+        <v>7.04793289332583</v>
       </c>
       <c r="D9" t="n">
-        <v>43.58831148126824</v>
+        <v>7.08310061570609</v>
       </c>
       <c r="E9" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F9" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.78989853260552</v>
+        <v>5.165858511548397</v>
       </c>
       <c r="D10" t="n">
-        <v>31.90181432929935</v>
+        <v>5.184044828511144</v>
       </c>
       <c r="E10" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F10" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.79915578748604</v>
+        <v>4.029862815466482</v>
       </c>
       <c r="D11" t="n">
-        <v>25.03500892509702</v>
+        <v>4.068188950328267</v>
       </c>
       <c r="E11" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F11" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.02554671444706</v>
+        <v>8.291651341097648</v>
       </c>
       <c r="D12" t="n">
-        <v>50.9115795629676</v>
+        <v>8.273131678982235</v>
       </c>
       <c r="E12" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F12" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.87113848495681</v>
+        <v>3.716560003805481</v>
       </c>
       <c r="D13" t="n">
-        <v>23.19442367676467</v>
+        <v>3.76909384747426</v>
       </c>
       <c r="E13" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F13" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.22673654933013</v>
+        <v>5.724344689266147</v>
       </c>
       <c r="D14" t="n">
-        <v>35.58745692685945</v>
+        <v>5.782961750614661</v>
       </c>
       <c r="E14" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F14" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.64588413193527</v>
+        <v>6.767456171439481</v>
       </c>
       <c r="D15" t="n">
-        <v>41.07531575783068</v>
+        <v>6.674738810647486</v>
       </c>
       <c r="E15" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F15" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.26273726153854</v>
+        <v>6.217694805000013</v>
       </c>
       <c r="D16" t="n">
-        <v>38.06957105878746</v>
+        <v>6.186305297052963</v>
       </c>
       <c r="E16" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F16" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.64662127196852</v>
+        <v>4.492575956694884</v>
       </c>
       <c r="D17" t="n">
-        <v>27.87921861615671</v>
+        <v>4.530373025125465</v>
       </c>
       <c r="E17" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F17" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>46.54642368399401</v>
+        <v>7.563793848649026</v>
       </c>
       <c r="D18" t="n">
-        <v>46.81141895636108</v>
+        <v>7.606855580408676</v>
       </c>
       <c r="E18" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F18" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>28.2922015164614</v>
+        <v>4.597482746424978</v>
       </c>
       <c r="D19" t="n">
-        <v>27.96145418079976</v>
+        <v>4.543736304379961</v>
       </c>
       <c r="E19" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F19" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>43.14079144083779</v>
+        <v>7.010378609136141</v>
       </c>
       <c r="D20" t="n">
-        <v>42.80605492855369</v>
+        <v>6.955983925889974</v>
       </c>
       <c r="E20" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F20" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>70.55120797904009</v>
+        <v>11.46457129659401</v>
       </c>
       <c r="D21" t="n">
-        <v>50.54585709064084</v>
+        <v>8.213701777229137</v>
       </c>
       <c r="E21" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F21" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>36.51390346645681</v>
+        <v>5.933509313299232</v>
       </c>
       <c r="D22" t="n">
-        <v>36.26623748772869</v>
+        <v>5.893263591755912</v>
       </c>
       <c r="E22" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F22" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>61.51204686430906</v>
+        <v>9.995707615450224</v>
       </c>
       <c r="D23" t="n">
-        <v>61.13273346779968</v>
+        <v>9.934069188517448</v>
       </c>
       <c r="E23" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F23" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>58.61429149992734</v>
+        <v>9.524822368738192</v>
       </c>
       <c r="D24" t="n">
-        <v>58.5895942146446</v>
+        <v>9.520809059879747</v>
       </c>
       <c r="E24" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F24" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>90.28074073674809</v>
+        <v>14.67062036972156</v>
       </c>
       <c r="D25" t="n">
-        <v>76.67034037191721</v>
+        <v>12.45893031043655</v>
       </c>
       <c r="E25" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F25" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>52.98350047791661</v>
+        <v>8.609818827661449</v>
       </c>
       <c r="D26" t="n">
-        <v>52.66093443309907</v>
+        <v>8.557401845378598</v>
       </c>
       <c r="E26" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F26" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>81.63331042865133</v>
+        <v>13.26541294465584</v>
       </c>
       <c r="D27" t="n">
-        <v>81.67361136602933</v>
+        <v>13.27196184697977</v>
       </c>
       <c r="E27" t="n">
-        <v>23.07094651699391</v>
+        <v>3.749028809011511</v>
       </c>
       <c r="F27" t="n">
-        <v>21.44068988683164</v>
+        <v>3.484112106610141</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
